--- a/artfynd/A 67528-2021 artfynd.xlsx
+++ b/artfynd/A 67528-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 67528-2021 artfynd.xlsx
+++ b/artfynd/A 67528-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>112551580</v>
       </c>
       <c r="B2" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,59 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112551568</v>
+        <v>112551576</v>
       </c>
       <c r="B3" t="n">
-        <v>55732</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Öster Boviggen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>378061</v>
+        <v>378192</v>
       </c>
       <c r="R3" t="n">
-        <v>6701300</v>
+        <v>6701587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,16 +872,11 @@
         <v>112551578</v>
       </c>
       <c r="B4" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -928,7 +904,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>378490</v>
+        <v>378489</v>
       </c>
       <c r="R4" t="n">
         <v>6701041</v>
@@ -990,19 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112551576</v>
+        <v>112551594</v>
       </c>
       <c r="B5" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1030,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>378192</v>
+        <v>378071</v>
       </c>
       <c r="R5" t="n">
-        <v>6701587</v>
+        <v>6701494</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,50 +1063,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112551594</v>
+        <v>112551568</v>
       </c>
       <c r="B6" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Öster Boviggen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>378071</v>
+        <v>378061</v>
       </c>
       <c r="R6" t="n">
-        <v>6701494</v>
+        <v>6701300</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 67528-2021 artfynd.xlsx
+++ b/artfynd/A 67528-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551580</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551578</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551594</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,8 +1191,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112551568</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>